--- a/tester.xlsx
+++ b/tester.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a24d1f46c5e1c0e4/Documents/www/base-camp/base-camp6/html/_repo/pwdstrength/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\richa\Documents\GitHub\pwdstrength\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="109" documentId="8_{4481B6EB-8C7C-4FC9-AD70-ED219D215F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF72AF1A-C4F9-4869-85BA-F16FA48CFE6F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC339D6-AE4E-4479-A668-2878538D31EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{1241A073-5CF3-49A6-96B8-7D50E6754806}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1241A073-5CF3-49A6-96B8-7D50E6754806}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -130,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -146,13 +146,32 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="11">
     <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -171,22 +190,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -229,173 +232,8 @@
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
+        <c:scatterStyle val="smoothMarker"/>
         <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$E$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>entropy</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$D$4:$D$20</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>16</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$E$4:$E$20</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="17"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>6.5999128421871278</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>13.199825684374256</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>19.799738526561384</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>26.399651368748511</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>32.999564210935638</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>39.599477053122769</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>46.199389895309892</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>52.799302737497023</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>59.399215579684153</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>65.999128421871276</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>72.5990412640584</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>79.198954106245537</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>85.798866948432661</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>92.398779790619784</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>98.998692632806922</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>105.59860547499405</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0D43-4E22-92BE-3D60CDE835B8}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
@@ -420,19 +258,7 @@
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
+            <c:symbol val="none"/>
           </c:marker>
           <c:xVal>
             <c:numRef>
@@ -498,63 +324,63 @@
             <c:numRef>
               <c:f>Sheet1!$F$4:$F$20</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.4875537940816872</c:v>
+                  <c:v>1.5286180733165751</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.587364739647068</c:v>
+                  <c:v>4.3235848219458592</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>14.547171078556012</c:v>
+                  <c:v>7.9429325050570689</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>21.144572249143224</c:v>
+                  <c:v>12.228944586532599</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>28.260635313496774</c:v>
+                  <c:v>17.090469617853099</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>35.819336806673959</c:v>
+                  <c:v>22.466005747331621</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>43.767160050471666</c:v>
+                  <c:v>28.31040290116049</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>52.064043994201263</c:v>
+                  <c:v>34.588678575566888</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>60.678687379071278</c:v>
+                  <c:v>41.272687979547513</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>69.585846567579225</c:v>
+                  <c:v>48.339147841786364</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>78.764660581454834</c:v>
+                  <c:v>55.76837856641766</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>88.197552798513172</c:v>
+                  <c:v>63.543460040456509</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>97.869478267879529</c:v>
+                  <c:v>71.649640971270458</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>107.76738916822201</c:v>
+                  <c:v>80.073911478135571</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>117.87984385839994</c:v>
+                  <c:v>88.804685110001472</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>128.19671379920965</c:v>
+                  <c:v>97.831556692260804</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-0D43-4E22-92BE-3D60CDE835B8}"/>
@@ -571,6 +397,173 @@
         </c:dLbls>
         <c:axId val="896027568"/>
         <c:axId val="621407088"/>
+      </c:scatterChart>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$E$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>entropy</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$D$4:$D$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$E$4:$E$20</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.7004397181410926</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.4008794362821853</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14.101319154423278</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>18.801758872564371</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>23.502198590705461</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>28.202638308846556</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>32.903078026987643</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>37.603517745128741</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>42.303957463269832</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>47.004397181410923</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>51.704836899552021</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>56.405276617693112</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>61.105716335834195</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>65.806156053975286</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>70.506595772116384</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>75.207035490257482</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0D43-4E22-92BE-3D60CDE835B8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="708996015"/>
+        <c:axId val="708992175"/>
       </c:scatterChart>
       <c:valAx>
         <c:axId val="896027568"/>
@@ -639,6 +632,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -656,7 +650,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -695,6 +689,72 @@
         </c:txPr>
         <c:crossAx val="896027568"/>
         <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="708992175"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="96"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="708996015"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="16"/>
+        <c:minorUnit val="4"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="708996015"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="708992175"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
@@ -1344,13 +1404,13 @@
   <autoFilter ref="D3:G20" xr:uid="{96B3B487-E7C2-419B-ADC8-E60805B31502}"/>
   <tableColumns count="4">
     <tableColumn id="3" xr3:uid="{94E688CF-59A3-45DD-9D42-13175B67F354}" name="strlen" dataDxfId="8"/>
-    <tableColumn id="1" xr3:uid="{6A0AE597-A356-47BB-92A9-366BA9A90B9D}" name="entropy" dataDxfId="6">
+    <tableColumn id="1" xr3:uid="{6A0AE597-A356-47BB-92A9-366BA9A90B9D}" name="entropy" dataDxfId="2">
       <calculatedColumnFormula>LOG(size^Table1[[#This Row],[strlen]], 2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{DE101A8F-8A1F-49D9-8A14-4FC5D2F4CDE9}" name="score" dataDxfId="7">
-      <calculatedColumnFormula>mul * E4^pwr</calculatedColumnFormula>
+    <tableColumn id="2" xr3:uid="{DE101A8F-8A1F-49D9-8A14-4FC5D2F4CDE9}" name="score" dataDxfId="0">
+      <calculatedColumnFormula xml:space="preserve"> mul*Table1[[#This Row],[entropy]]^pwr</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{905BFEFF-0194-436A-AD03-5DC43FB43DA6}" name="strength" dataDxfId="0">
+    <tableColumn id="5" xr3:uid="{905BFEFF-0194-436A-AD03-5DC43FB43DA6}" name="strength" dataDxfId="1">
       <calculatedColumnFormula>ROUND(Table1[[#This Row],[score]]/20,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1359,11 +1419,11 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F3B74D6C-135F-40E9-876A-0FDFA1421B30}" name="Table2" displayName="Table2" ref="D23:F29" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F3B74D6C-135F-40E9-876A-0FDFA1421B30}" name="Table2" displayName="Table2" ref="D23:F29" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
   <autoFilter ref="D23:F29" xr:uid="{F3B74D6C-135F-40E9-876A-0FDFA1421B30}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{ABD7F27A-6A79-471F-9471-7767A7E66DD7}" name="entropy" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{C5953E64-853D-4FEF-B544-B494F9D60C06}" name="label" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{ABD7F27A-6A79-471F-9471-7767A7E66DD7}" name="entropy" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{C5953E64-853D-4FEF-B544-B494F9D60C06}" name="label" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{59E0F959-0BFB-4448-BECB-7DF0454927C8}" name="strength" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1688,23 +1748,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939F591A-D8AB-4DA1-9480-A257A9B548A1}">
   <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.28515625" customWidth="1"/>
-    <col min="2" max="2" width="7.85546875" customWidth="1"/>
-    <col min="3" max="3" width="5.140625" customWidth="1"/>
+    <col min="1" max="1" width="8.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.88671875" customWidth="1"/>
+    <col min="3" max="3" width="5.109375" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="14" style="3" customWidth="1"/>
     <col min="6" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="str">
         <f>"$score = ($entropy ** "&amp;pwr&amp;") * "&amp;mul&amp;";"</f>
-        <v>$score = ($entropy ** 1.3) * 0.3;</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>$score = ($entropy ** 1.5) * 0.15;</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1718,12 +1778,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="6">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -1732,8 +1792,8 @@
         <f>LOG(size^Table1[[#This Row],[strlen]], 2)</f>
         <v>0</v>
       </c>
-      <c r="F4" s="2">
-        <f>mul * E4^pwr</f>
+      <c r="F4" s="4">
+        <f xml:space="preserve"> mul*Table1[[#This Row],[entropy]]^pwr</f>
         <v>0</v>
       </c>
       <c r="G4" s="1">
@@ -1741,296 +1801,303 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="6">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
       </c>
       <c r="E5" s="2">
         <f>LOG(size^Table1[[#This Row],[strlen]], 2)</f>
-        <v>6.5999128421871278</v>
-      </c>
-      <c r="F5" s="2">
-        <f>mul * E5^pwr</f>
-        <v>3.4875537940816872</v>
+        <v>4.7004397181410926</v>
+      </c>
+      <c r="F5" s="4">
+        <f xml:space="preserve"> mul*Table1[[#This Row],[entropy]]^pwr</f>
+        <v>1.5286180733165751</v>
       </c>
       <c r="G5" s="1">
         <f>ROUND(Table1[[#This Row],[score]]/20,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D6" s="1">
         <v>2</v>
       </c>
       <c r="E6" s="2">
         <f>LOG(size^Table1[[#This Row],[strlen]], 2)</f>
-        <v>13.199825684374256</v>
-      </c>
-      <c r="F6" s="2">
-        <f>mul * E6^pwr</f>
-        <v>8.587364739647068</v>
+        <v>9.4008794362821853</v>
+      </c>
+      <c r="F6" s="4">
+        <f xml:space="preserve"> mul*Table1[[#This Row],[entropy]]^pwr</f>
+        <v>4.3235848219458592</v>
       </c>
       <c r="G6" s="1">
         <f>ROUND(Table1[[#This Row],[score]]/20,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="6">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
       </c>
       <c r="E7" s="2">
         <f>LOG(size^Table1[[#This Row],[strlen]], 2)</f>
-        <v>19.799738526561384</v>
-      </c>
-      <c r="F7" s="2">
-        <f>mul * E7^pwr</f>
-        <v>14.547171078556012</v>
+        <v>14.101319154423278</v>
+      </c>
+      <c r="F7" s="4">
+        <f xml:space="preserve"> mul*Table1[[#This Row],[entropy]]^pwr</f>
+        <v>7.9429325050570689</v>
       </c>
       <c r="G7" s="1">
         <f>ROUND(Table1[[#This Row],[score]]/20,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D8" s="1">
         <v>4</v>
       </c>
       <c r="E8" s="2">
         <f>LOG(size^Table1[[#This Row],[strlen]], 2)</f>
-        <v>26.399651368748511</v>
-      </c>
-      <c r="F8" s="2">
-        <f>mul * E8^pwr</f>
-        <v>21.144572249143224</v>
+        <v>18.801758872564371</v>
+      </c>
+      <c r="F8" s="4">
+        <f xml:space="preserve"> mul*Table1[[#This Row],[entropy]]^pwr</f>
+        <v>12.228944586532599</v>
       </c>
       <c r="G8" s="1">
         <f>ROUND(Table1[[#This Row],[score]]/20,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D9" s="1">
         <v>5</v>
       </c>
       <c r="E9" s="2">
         <f>LOG(size^Table1[[#This Row],[strlen]], 2)</f>
-        <v>32.999564210935638</v>
-      </c>
-      <c r="F9" s="2">
-        <f>mul * E9^pwr</f>
-        <v>28.260635313496774</v>
+        <v>23.502198590705461</v>
+      </c>
+      <c r="F9" s="4">
+        <f xml:space="preserve"> mul*Table1[[#This Row],[entropy]]^pwr</f>
+        <v>17.090469617853099</v>
       </c>
       <c r="G9" s="1">
         <f>ROUND(Table1[[#This Row],[score]]/20,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D10" s="1">
         <v>6</v>
       </c>
       <c r="E10" s="2">
         <f>LOG(size^Table1[[#This Row],[strlen]], 2)</f>
-        <v>39.599477053122769</v>
-      </c>
-      <c r="F10" s="2">
-        <f>mul * E10^pwr</f>
-        <v>35.819336806673959</v>
+        <v>28.202638308846556</v>
+      </c>
+      <c r="F10" s="4">
+        <f xml:space="preserve"> mul*Table1[[#This Row],[entropy]]^pwr</f>
+        <v>22.466005747331621</v>
       </c>
       <c r="G10" s="1">
         <f>ROUND(Table1[[#This Row],[score]]/20,0)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D11" s="1">
         <v>7</v>
       </c>
       <c r="E11" s="2">
         <f>LOG(size^Table1[[#This Row],[strlen]], 2)</f>
-        <v>46.199389895309892</v>
-      </c>
-      <c r="F11" s="2">
-        <f>mul * E11^pwr</f>
-        <v>43.767160050471666</v>
+        <v>32.903078026987643</v>
+      </c>
+      <c r="F11" s="4">
+        <f xml:space="preserve"> mul*Table1[[#This Row],[entropy]]^pwr</f>
+        <v>28.31040290116049</v>
       </c>
       <c r="G11" s="1">
         <f>ROUND(Table1[[#This Row],[score]]/20,0)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D12" s="1">
         <v>8</v>
       </c>
       <c r="E12" s="2">
         <f>LOG(size^Table1[[#This Row],[strlen]], 2)</f>
-        <v>52.799302737497023</v>
-      </c>
-      <c r="F12" s="2">
-        <f>mul * E12^pwr</f>
-        <v>52.064043994201263</v>
+        <v>37.603517745128741</v>
+      </c>
+      <c r="F12" s="4">
+        <f xml:space="preserve"> mul*Table1[[#This Row],[entropy]]^pwr</f>
+        <v>34.588678575566888</v>
       </c>
       <c r="G12" s="1">
         <f>ROUND(Table1[[#This Row],[score]]/20,0)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D13" s="1">
         <v>9</v>
       </c>
       <c r="E13" s="2">
         <f>LOG(size^Table1[[#This Row],[strlen]], 2)</f>
-        <v>59.399215579684153</v>
-      </c>
-      <c r="F13" s="2">
-        <f>mul * E13^pwr</f>
-        <v>60.678687379071278</v>
+        <v>42.303957463269832</v>
+      </c>
+      <c r="F13" s="4">
+        <f xml:space="preserve"> mul*Table1[[#This Row],[entropy]]^pwr</f>
+        <v>41.272687979547513</v>
       </c>
       <c r="G13" s="1">
         <f>ROUND(Table1[[#This Row],[score]]/20,0)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D14" s="1">
         <v>10</v>
       </c>
       <c r="E14" s="2">
         <f>LOG(size^Table1[[#This Row],[strlen]], 2)</f>
-        <v>65.999128421871276</v>
-      </c>
-      <c r="F14" s="2">
-        <f>mul * E14^pwr</f>
-        <v>69.585846567579225</v>
+        <v>47.004397181410923</v>
+      </c>
+      <c r="F14" s="4">
+        <f xml:space="preserve"> mul*Table1[[#This Row],[entropy]]^pwr</f>
+        <v>48.339147841786364</v>
       </c>
       <c r="G14" s="1">
         <f>ROUND(Table1[[#This Row],[score]]/20,0)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D15" s="1">
         <v>11</v>
       </c>
       <c r="E15" s="2">
         <f>LOG(size^Table1[[#This Row],[strlen]], 2)</f>
-        <v>72.5990412640584</v>
-      </c>
-      <c r="F15" s="2">
-        <f>mul * E15^pwr</f>
-        <v>78.764660581454834</v>
+        <v>51.704836899552021</v>
+      </c>
+      <c r="F15" s="4">
+        <f xml:space="preserve"> mul*Table1[[#This Row],[entropy]]^pwr</f>
+        <v>55.76837856641766</v>
       </c>
       <c r="G15" s="1">
         <f>ROUND(Table1[[#This Row],[score]]/20,0)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D16" s="1">
         <v>12</v>
       </c>
       <c r="E16" s="2">
         <f>LOG(size^Table1[[#This Row],[strlen]], 2)</f>
-        <v>79.198954106245537</v>
-      </c>
-      <c r="F16" s="2">
-        <f>mul * E16^pwr</f>
-        <v>88.197552798513172</v>
+        <v>56.405276617693112</v>
+      </c>
+      <c r="F16" s="4">
+        <f xml:space="preserve"> mul*Table1[[#This Row],[entropy]]^pwr</f>
+        <v>63.543460040456509</v>
       </c>
       <c r="G16" s="1">
         <f>ROUND(Table1[[#This Row],[score]]/20,0)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="4:7" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D17" s="1">
         <v>13</v>
       </c>
       <c r="E17" s="2">
         <f>LOG(size^Table1[[#This Row],[strlen]], 2)</f>
-        <v>85.798866948432661</v>
-      </c>
-      <c r="F17" s="2">
-        <f>mul * E17^pwr</f>
-        <v>97.869478267879529</v>
+        <v>61.105716335834195</v>
+      </c>
+      <c r="F17" s="4">
+        <f xml:space="preserve"> mul*Table1[[#This Row],[entropy]]^pwr</f>
+        <v>71.649640971270458</v>
       </c>
       <c r="G17" s="1">
         <f>ROUND(Table1[[#This Row],[score]]/20,0)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D18" s="1">
         <v>14</v>
       </c>
       <c r="E18" s="2">
         <f>LOG(size^Table1[[#This Row],[strlen]], 2)</f>
-        <v>92.398779790619784</v>
-      </c>
-      <c r="F18" s="2">
-        <f>mul * E18^pwr</f>
-        <v>107.76738916822201</v>
+        <v>65.806156053975286</v>
+      </c>
+      <c r="F18" s="4">
+        <f xml:space="preserve"> mul*Table1[[#This Row],[entropy]]^pwr</f>
+        <v>80.073911478135571</v>
       </c>
       <c r="G18" s="1">
         <f>ROUND(Table1[[#This Row],[score]]/20,0)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="4:7" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D19" s="1">
         <v>15</v>
       </c>
       <c r="E19" s="2">
         <f>LOG(size^Table1[[#This Row],[strlen]], 2)</f>
-        <v>98.998692632806922</v>
-      </c>
-      <c r="F19" s="2">
-        <f>mul * E19^pwr</f>
-        <v>117.87984385839994</v>
+        <v>70.506595772116384</v>
+      </c>
+      <c r="F19" s="4">
+        <f xml:space="preserve"> mul*Table1[[#This Row],[entropy]]^pwr</f>
+        <v>88.804685110001472</v>
       </c>
       <c r="G19" s="1">
         <f>ROUND(Table1[[#This Row],[score]]/20,0)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D20" s="1">
         <v>16</v>
       </c>
       <c r="E20" s="2">
         <f>LOG(size^Table1[[#This Row],[strlen]], 2)</f>
-        <v>105.59860547499405</v>
-      </c>
-      <c r="F20" s="2">
-        <f>mul * E20^pwr</f>
-        <v>128.19671379920965</v>
+        <v>75.207035490257482</v>
+      </c>
+      <c r="F20" s="4">
+        <f xml:space="preserve"> mul*Table1[[#This Row],[entropy]]^pwr</f>
+        <v>97.831556692260804</v>
       </c>
       <c r="G20" s="1">
         <f>ROUND(Table1[[#This Row],[score]]/20,0)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="4:7" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D21" s="1"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="7"/>
+    </row>
+    <row r="22" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="23" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="G22" s="7"/>
+    </row>
+    <row r="23" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D23" s="4" t="s">
         <v>0</v>
       </c>
@@ -2041,7 +2108,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D24" s="5">
         <v>0</v>
       </c>
@@ -2052,7 +2119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D25" s="5">
         <v>16</v>
       </c>
@@ -2063,7 +2130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D26" s="5">
         <v>24</v>
       </c>
@@ -2074,7 +2141,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D27" s="5">
         <v>36</v>
       </c>
@@ -2085,7 +2152,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D28" s="5">
         <v>54</v>
       </c>
@@ -2096,7 +2163,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D29" s="5">
         <v>64</v>
       </c>
